--- a/Data Analysis/1_Data/soc_dominance_2002_2017.xlsx
+++ b/Data Analysis/1_Data/soc_dominance_2002_2017.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -405,6 +405,11 @@
           <t>Corg_val_diff</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>block</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -443,6 +448,11 @@
       <c r="J2">
         <v>848.8764879999983</v>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -481,6 +491,11 @@
       <c r="J3">
         <v>1096.1901727</v>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -519,6 +534,11 @@
       <c r="J4">
         <v>447.2937850000007</v>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -557,6 +577,11 @@
       <c r="J5">
         <v>-194.9398349999993</v>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -595,6 +620,11 @@
       <c r="J6">
         <v>-194.6454993249984</v>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -633,6 +663,11 @@
       <c r="J7">
         <v>600.3867187249998</v>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -671,6 +706,11 @@
       <c r="J8">
         <v>-1.691360725000656</v>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -709,6 +749,11 @@
       <c r="J9">
         <v>141.5645757499995</v>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -747,6 +792,11 @@
       <c r="J10">
         <v>749.8983729500003</v>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -785,6 +835,11 @@
       <c r="J11">
         <v>1251.405361999999</v>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -823,6 +878,11 @@
       <c r="J12">
         <v>-281.6896307999986</v>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -861,6 +921,11 @@
       <c r="J13">
         <v>-371.824670399999</v>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -899,6 +964,11 @@
       <c r="J14">
         <v>1308.6591751</v>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -937,6 +1007,11 @@
       <c r="J15">
         <v>-100.5679001000011</v>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -975,6 +1050,11 @@
       <c r="J16">
         <v>538.6719435999995</v>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1013,6 +1093,11 @@
       <c r="J17">
         <v>904.6552174000002</v>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1051,6 +1136,11 @@
       <c r="J18">
         <v>1421.384213550001</v>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1089,6 +1179,11 @@
       <c r="J19">
         <v>21.21688885000088</v>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1127,6 +1222,11 @@
       <c r="J20">
         <v>379.7759349999988</v>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1165,6 +1265,11 @@
       <c r="J21">
         <v>1148.66538</v>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1203,6 +1308,11 @@
       <c r="J22">
         <v>1562.104470000002</v>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1241,6 +1351,11 @@
       <c r="J23">
         <v>-623.7500099999995</v>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1279,6 +1394,11 @@
       <c r="J24">
         <v>1068.032042</v>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1317,6 +1437,11 @@
       <c r="J25">
         <v>1368.7642868</v>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1355,6 +1480,11 @@
       <c r="J26">
         <v>640.8192251999998</v>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1393,6 +1523,11 @@
       <c r="J27">
         <v>811.2153564000007</v>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1431,6 +1566,11 @@
       <c r="J28">
         <v>-30.85797240000005</v>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1469,6 +1609,11 @@
       <c r="J29">
         <v>1124.64297</v>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1507,6 +1652,11 @@
       <c r="J30">
         <v>-93.17806424999823</v>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1545,6 +1695,11 @@
       <c r="J31">
         <v>779.0276968500004</v>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1583,6 +1738,11 @@
       <c r="J32">
         <v>-851.933382525002</v>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1621,6 +1781,11 @@
       <c r="J33">
         <v>746.4886406999993</v>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1659,6 +1824,11 @@
       <c r="J34">
         <v>920.7122443500004</v>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1697,6 +1867,11 @@
       <c r="J35">
         <v>-98.86338320000117</v>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1735,6 +1910,11 @@
       <c r="J36">
         <v>1545.549039500002</v>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1773,6 +1953,11 @@
       <c r="J37">
         <v>-546.7792035000001</v>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1811,6 +1996,11 @@
       <c r="J38">
         <v>-1199.031372000001</v>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1849,6 +2039,11 @@
       <c r="J39">
         <v>1188.650147999999</v>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1887,6 +2082,11 @@
       <c r="J40">
         <v>-18.36298859999903</v>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1925,6 +2125,11 @@
       <c r="J41">
         <v>806.3512347000011</v>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1963,6 +2168,11 @@
       <c r="J42">
         <v>279.4709388000008</v>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2001,6 +2211,11 @@
       <c r="J43">
         <v>7.34028554999968</v>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2039,6 +2254,11 @@
       <c r="J44">
         <v>820.650726600002</v>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2077,6 +2297,11 @@
       <c r="J45">
         <v>432.6917605500009</v>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2115,6 +2340,11 @@
       <c r="J46">
         <v>1572.698400999998</v>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2153,6 +2383,11 @@
       <c r="J47">
         <v>654.3563513000011</v>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2191,6 +2426,11 @@
       <c r="J48">
         <v>850.057600499999</v>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2229,6 +2469,11 @@
       <c r="J49">
         <v>1612.6440375</v>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2267,6 +2512,11 @@
       <c r="J50">
         <v>213.6283439999989</v>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2305,6 +2555,11 @@
       <c r="J51">
         <v>1337.323300799999</v>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2343,6 +2598,11 @@
       <c r="J52">
         <v>1251.921299999999</v>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2381,6 +2641,11 @@
       <c r="J53">
         <v>708.2651562000004</v>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2419,6 +2684,11 @@
       <c r="J54">
         <v>2015.272530600002</v>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2457,6 +2727,11 @@
       <c r="J55">
         <v>1782.373585099998</v>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2495,6 +2770,11 @@
       <c r="J56">
         <v>219.0162665999989</v>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2533,6 +2813,11 @@
       <c r="J57">
         <v>1486.9453818</v>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2571,6 +2856,11 @@
       <c r="J58">
         <v>783.5731697999988</v>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2609,6 +2899,11 @@
       <c r="J59">
         <v>1416.143377199998</v>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2647,6 +2942,11 @@
       <c r="J60">
         <v>1689.436016399997</v>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2685,6 +2985,11 @@
       <c r="J61">
         <v>1809.685365199999</v>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2723,6 +3028,11 @@
       <c r="J62">
         <v>1320.702264799997</v>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2761,6 +3071,11 @@
       <c r="J63">
         <v>250.1567544</v>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2799,6 +3114,11 @@
       <c r="J64">
         <v>1955.756904599998</v>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2837,6 +3157,11 @@
       <c r="J65">
         <v>-160.8970769999985</v>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2866,6 +3191,11 @@
       <c r="H66">
         <v>88865.44416000003</v>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2904,6 +3234,11 @@
       <c r="J67">
         <v>520.1578823999977</v>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2942,6 +3277,11 @@
       <c r="J68">
         <v>1637.489703499997</v>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2980,6 +3320,11 @@
       <c r="J69">
         <v>1636.760564399999</v>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3018,6 +3363,11 @@
       <c r="J70">
         <v>2211.232846799998</v>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3056,6 +3406,11 @@
       <c r="J71">
         <v>1562.0473557</v>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3094,6 +3449,11 @@
       <c r="J72">
         <v>939.7552152</v>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3132,6 +3492,11 @@
       <c r="J73">
         <v>2302.872896699998</v>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3170,6 +3535,11 @@
       <c r="J74">
         <v>341.0062992000011</v>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3208,6 +3578,11 @@
       <c r="J75">
         <v>1562.45056875</v>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3246,6 +3621,11 @@
       <c r="J76">
         <v>641.2431538499989</v>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3284,6 +3664,11 @@
       <c r="J77">
         <v>1510.032872249998</v>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3322,6 +3707,11 @@
       <c r="J78">
         <v>1489.201616249998</v>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3360,6 +3750,11 @@
       <c r="J79">
         <v>990.509368499998</v>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3398,6 +3793,11 @@
       <c r="J80">
         <v>2733.697819350003</v>
       </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3436,6 +3836,11 @@
       <c r="J81">
         <v>1446.081326250001</v>
       </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3474,6 +3879,11 @@
       <c r="J82">
         <v>1995.616802550001</v>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3512,6 +3922,11 @@
       <c r="J83">
         <v>1571.210138249999</v>
       </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3550,6 +3965,11 @@
       <c r="J84">
         <v>693.3132113500003</v>
       </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3588,6 +4008,11 @@
       <c r="J85">
         <v>1202.667874800002</v>
       </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3626,6 +4051,11 @@
       <c r="J86">
         <v>2619.213266400002</v>
       </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3664,6 +4094,11 @@
       <c r="J87">
         <v>705.5697400500009</v>
       </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3702,6 +4137,11 @@
       <c r="J88">
         <v>748.1880854500001</v>
       </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3740,6 +4180,11 @@
       <c r="J89">
         <v>2198.279371750002</v>
       </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3778,6 +4223,11 @@
       <c r="J90">
         <v>1791.712007999999</v>
       </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3816,6 +4266,11 @@
       <c r="J91">
         <v>1829.000819999999</v>
       </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3854,6 +4309,11 @@
       <c r="J92">
         <v>651.1674359999995</v>
       </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3892,6 +4352,11 @@
       <c r="J93">
         <v>1842.406301999999</v>
       </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3929,6 +4394,11 @@
       </c>
       <c r="J94">
         <v>2028.234017999999</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
       </c>
     </row>
   </sheetData>
